--- a/eval/qlora/evaluation_metrics.xlsx
+++ b/eval/qlora/evaluation_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,35 +525,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R16</t>
+          <t>Llama3.1-70B R8</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2400</v>
       </c>
       <c r="C3" t="n">
-        <v>0.875</v>
+        <v>0.8404166666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9292343387470998</v>
+        <v>0.8173913043478261</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7701923076923077</v>
+        <v>0.8134615384615385</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8422712933753943</v>
+        <v>0.8154216867469881</v>
       </c>
       <c r="G3" t="n">
-        <v>801</v>
+        <v>846</v>
       </c>
       <c r="H3" t="n">
-        <v>1299</v>
+        <v>1171</v>
       </c>
       <c r="I3" t="n">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="J3" t="n">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -562,35 +562,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Llama3.1-70B R32</t>
+          <t>Llama3.1-70B R16</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2400</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8295833333333333</v>
+        <v>0.875</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9102730819245773</v>
+        <v>0.9292343387470998</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6730769230769231</v>
+        <v>0.7701923076923077</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7739082365948039</v>
+        <v>0.8422712933753943</v>
       </c>
       <c r="G4" t="n">
-        <v>700</v>
+        <v>801</v>
       </c>
       <c r="H4" t="n">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="I4" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>239</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -599,35 +599,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Llama3.1-8B FT</t>
+          <t>Llama3.1-70B R32</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2400</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7870833333333334</v>
+        <v>0.8295833333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8816738816738817</v>
+        <v>0.9102730819245773</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5875</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="F5" t="n">
-        <v>0.705135603000577</v>
+        <v>0.7739082365948039</v>
       </c>
       <c r="G5" t="n">
-        <v>611</v>
+        <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>1278</v>
+        <v>1291</v>
       </c>
       <c r="I5" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="J5" t="n">
-        <v>429</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -636,35 +636,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R16</t>
+          <t>Llama3.1-8B FT</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2400</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8029166666666666</v>
+        <v>0.7870833333333334</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8816738816738817</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6490384615384616</v>
+        <v>0.5875</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7405375754251234</v>
+        <v>0.705135603000577</v>
       </c>
       <c r="G6" t="n">
-        <v>675</v>
+        <v>611</v>
       </c>
       <c r="H6" t="n">
-        <v>1252</v>
+        <v>1278</v>
       </c>
       <c r="I6" t="n">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="J6" t="n">
-        <v>365</v>
+        <v>429</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
@@ -673,38 +673,112 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Llama3.1-8B R32</t>
+          <t>Llama3.1-8B R8</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2400</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8020833333333334</v>
+        <v>0.7966666666666666</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8626444159178434</v>
+        <v>0.8484848484848485</v>
       </c>
       <c r="E7" t="n">
         <v>0.6461538461538462</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7388675096206707</v>
+        <v>0.7336244541484717</v>
       </c>
       <c r="G7" t="n">
         <v>672</v>
       </c>
       <c r="H7" t="n">
-        <v>1253</v>
+        <v>1240</v>
       </c>
       <c r="I7" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="J7" t="n">
         <v>368</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R16</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8029166666666666</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6490384615384616</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7405375754251234</v>
+      </c>
+      <c r="G8" t="n">
+        <v>675</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1252</v>
+      </c>
+      <c r="I8" t="n">
+        <v>108</v>
+      </c>
+      <c r="J8" t="n">
+        <v>365</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B R32</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8020833333333334</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8626444159178434</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6461538461538462</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7388675096206707</v>
+      </c>
+      <c r="G9" t="n">
+        <v>672</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1253</v>
+      </c>
+      <c r="I9" t="n">
+        <v>107</v>
+      </c>
+      <c r="J9" t="n">
+        <v>368</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/eval/qlora/evaluation_metrics.xlsx
+++ b/eval/qlora/evaluation_metrics.xlsx
@@ -532,19 +532,19 @@
         <v>2400</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8404166666666667</v>
+        <v>0.8412500000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8173913043478261</v>
+        <v>0.8177434908389586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8134615384615385</v>
+        <v>0.8153846153846154</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8154216867469881</v>
+        <v>0.8165623495426095</v>
       </c>
       <c r="G3" t="n">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H3" t="n">
         <v>1171</v>
@@ -553,7 +553,7 @@
         <v>189</v>
       </c>
       <c r="J3" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -680,19 +680,19 @@
         <v>2400</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7966666666666666</v>
+        <v>0.7975</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.8488664987405542</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6461538461538462</v>
+        <v>0.6480769230769231</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7336244541484717</v>
+        <v>0.7350054525627044</v>
       </c>
       <c r="G7" t="n">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="H7" t="n">
         <v>1240</v>
@@ -701,7 +701,7 @@
         <v>120</v>
       </c>
       <c r="J7" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
